--- a/backend/data/Monthwise MW Report.xlsx
+++ b/backend/data/Monthwise MW Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Sep-24</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>Jul-26</t>
+  </si>
+  <si>
+    <t>Aug-26</t>
+  </si>
+  <si>
+    <t>Sep-26</t>
   </si>
   <si>
     <t>MONTH</t>
@@ -220,7 +226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8" customWidth="1"/>
@@ -238,37 +244,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -311,13 +317,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>475320.000</v>
+        <v>478680.000</v>
       </c>
       <c r="C3" s="2">
         <v>55200.000</v>
       </c>
       <c r="D3" s="2">
-        <v>566760.000</v>
+        <v>563400.000</v>
       </c>
       <c r="E3" s="2">
         <v>21840.000</v>
@@ -326,13 +332,13 @@
         <v>1119120.000</v>
       </c>
       <c r="G3" s="3">
-        <v>3.529290</v>
+        <v>3.554290</v>
       </c>
       <c r="H3" s="3">
         <v>0.397980</v>
       </c>
       <c r="I3" s="3">
-        <v>4.141180</v>
+        <v>4.116350</v>
       </c>
       <c r="J3" s="3">
         <v>0.154580</v>
@@ -346,13 +352,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>4935169.000</v>
+        <v>4935409.000</v>
       </c>
       <c r="C4" s="2">
         <v>186720.000</v>
       </c>
       <c r="D4" s="2">
-        <v>999830.000</v>
+        <v>999590.000</v>
       </c>
       <c r="E4" s="2">
         <v>67680.000</v>
@@ -361,19 +367,19 @@
         <v>6189399.000</v>
       </c>
       <c r="G4" s="3">
-        <v>37.303200</v>
+        <v>37.305430</v>
       </c>
       <c r="H4" s="3">
         <v>1.378050</v>
       </c>
       <c r="I4" s="3">
-        <v>7.455340</v>
+        <v>7.453430</v>
       </c>
       <c r="J4" s="3">
         <v>0.480280</v>
       </c>
       <c r="K4" s="2">
-        <v>46.619</v>
+        <v>46.618</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1046,34 +1052,104 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>16213850.000</v>
+        <v>21322730.000</v>
       </c>
       <c r="C24" s="2">
-        <v>105843.000</v>
+        <v>157783.000</v>
       </c>
       <c r="D24" s="2">
-        <v>1360397.000</v>
+        <v>1887177.000</v>
       </c>
       <c r="E24" s="2">
-        <v>89460.000</v>
+        <v>120120.000</v>
       </c>
       <c r="F24" s="2">
-        <v>17769550.000</v>
+        <v>23487810.000</v>
       </c>
       <c r="G24" s="3">
-        <v>126.460510</v>
+        <v>166.319720</v>
       </c>
       <c r="H24" s="3">
-        <v>0.821550</v>
+        <v>1.224400</v>
       </c>
       <c r="I24" s="3">
-        <v>10.504540</v>
+        <v>14.583140</v>
       </c>
       <c r="J24" s="3">
-        <v>0.683820</v>
+        <v>0.918140</v>
       </c>
       <c r="K24" s="2">
-        <v>138.470</v>
+        <v>183.045</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>19884300.000</v>
+      </c>
+      <c r="C25" s="2">
+        <v>141540.000</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2695120.000</v>
+      </c>
+      <c r="E25" s="2">
+        <v>188720.000</v>
+      </c>
+      <c r="F25" s="2">
+        <v>22909680.000</v>
+      </c>
+      <c r="G25" s="3">
+        <v>154.841020</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1.096320</v>
+      </c>
+      <c r="I25" s="3">
+        <v>20.769020</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1.441200</v>
+      </c>
+      <c r="K25" s="2">
+        <v>178.149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>11844120.000</v>
+      </c>
+      <c r="C26" s="2">
+        <v>93660.000</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1040620.000</v>
+      </c>
+      <c r="E26" s="2">
+        <v>130760.000</v>
+      </c>
+      <c r="F26" s="2">
+        <v>13109160.000</v>
+      </c>
+      <c r="G26" s="3">
+        <v>91.996840</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.724760</v>
+      </c>
+      <c r="I26" s="3">
+        <v>7.960220</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.998170</v>
+      </c>
+      <c r="K26" s="2">
+        <v>101.682</v>
       </c>
     </row>
   </sheetData>

--- a/backend/data/Monthwise MW Report.xlsx
+++ b/backend/data/Monthwise MW Report.xlsx
@@ -338,7 +338,7 @@
         <v>0.397980</v>
       </c>
       <c r="I3" s="3">
-        <v>4.116350</v>
+        <v>4.116460</v>
       </c>
       <c r="J3" s="3">
         <v>0.154580</v>
@@ -367,7 +367,7 @@
         <v>6189399.000</v>
       </c>
       <c r="G4" s="3">
-        <v>37.305430</v>
+        <v>37.305260</v>
       </c>
       <c r="H4" s="3">
         <v>1.378050</v>
@@ -1122,34 +1122,34 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>11844120.000</v>
+        <v>11868480.000</v>
       </c>
       <c r="C26" s="2">
         <v>93660.000</v>
       </c>
       <c r="D26" s="2">
-        <v>1040620.000</v>
+        <v>1048460.000</v>
       </c>
       <c r="E26" s="2">
         <v>130760.000</v>
       </c>
       <c r="F26" s="2">
-        <v>13109160.000</v>
+        <v>13141360.000</v>
       </c>
       <c r="G26" s="3">
-        <v>91.996840</v>
+        <v>92.186530</v>
       </c>
       <c r="H26" s="3">
         <v>0.724760</v>
       </c>
       <c r="I26" s="3">
-        <v>7.960220</v>
+        <v>8.020460</v>
       </c>
       <c r="J26" s="3">
         <v>0.998170</v>
       </c>
       <c r="K26" s="2">
-        <v>101.682</v>
+        <v>101.932</v>
       </c>
     </row>
   </sheetData>
